--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_7.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02473047139532392</v>
+        <v>0.01953950647997989</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008431038882939211</v>
+        <v>0.008426604091929184</v>
       </c>
       <c r="C2" t="n">
-        <v>44541567</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44541567</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>31025692</v>
+        <v>4201284</v>
       </c>
       <c r="L2" t="n">
-        <v>16864190</v>
+        <v>2056703</v>
       </c>
       <c r="M2" t="n">
-        <v>4030110</v>
+        <v>448520</v>
       </c>
       <c r="N2" t="n">
-        <v>194982</v>
+        <v>13372</v>
       </c>
       <c r="O2" t="n">
-        <v>2420851</v>
+        <v>261861</v>
       </c>
       <c r="P2" t="n">
-        <v>985859</v>
+        <v>101870</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999892711639404</v>
+        <v>0.9999880194664001</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8583281636238098</v>
+        <v>0.7988697290420532</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7293020486831665</v>
+        <v>0.631770133972168</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6576825976371765</v>
+        <v>0.5311015248298645</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2984675765037537</v>
+        <v>0.1094128414988518</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7157679200172424</v>
+        <v>0.5881186127662659</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7958376407623291</v>
+        <v>0.7120240926742554</v>
       </c>
       <c r="X2" t="n">
-        <v>44541567</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44541567</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>33971358</v>
+        <v>4822613</v>
       </c>
       <c r="AG2" t="n">
-        <v>21009908</v>
+        <v>3003787</v>
       </c>
       <c r="AH2" t="n">
-        <v>5618737</v>
+        <v>802859</v>
       </c>
       <c r="AI2" t="n">
-        <v>414498</v>
+        <v>59182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3217997</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260744</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563041925430298</v>
+        <v>0.9558094143867493</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114295840263367</v>
+        <v>0.9115616083145142</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8578492999076843</v>
+        <v>0.8578552603721619</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617420315742493</v>
+        <v>0.6612218618392944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019191265106201</v>
+        <v>0.9019814133644104</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314475059509277</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.006200706786678362</v>
+        <v>0.00477781638445617</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002020049719825228</v>
+        <v>0.00201955565764127</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>31025692</v>
+        <v>4201284</v>
       </c>
       <c r="E3" t="n">
-        <v>4311841</v>
+        <v>807651</v>
       </c>
       <c r="F3" t="n">
-        <v>117425</v>
+        <v>24558</v>
       </c>
       <c r="G3" t="n">
-        <v>15105</v>
+        <v>2090</v>
       </c>
       <c r="H3" t="n">
-        <v>6950</v>
+        <v>1390</v>
       </c>
       <c r="I3" t="n">
-        <v>482</v>
+        <v>81</v>
       </c>
       <c r="J3" t="n">
-        <v>70672356</v>
+        <v>10069544</v>
       </c>
       <c r="K3" t="n">
-        <v>74615922</v>
+        <v>10321191</v>
       </c>
       <c r="L3" t="n">
-        <v>85864872</v>
+        <v>11915363</v>
       </c>
       <c r="M3" t="n">
-        <v>106562055</v>
+        <v>15082932</v>
       </c>
       <c r="N3" t="n">
-        <v>114129169</v>
+        <v>16217521</v>
       </c>
       <c r="O3" t="n">
-        <v>110683246</v>
+        <v>15722147</v>
       </c>
       <c r="P3" t="n">
-        <v>113607631</v>
+        <v>16181292</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8745170831680298</v>
+        <v>0.8340749740600586</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7303683757781982</v>
+        <v>0.6228886842727661</v>
       </c>
       <c r="T3" t="n">
-        <v>0.614841639995575</v>
+        <v>0.4786362648010254</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3110078275203705</v>
+        <v>0.1491827964782715</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6781414151191711</v>
+        <v>0.5129882097244263</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7281844019889832</v>
+        <v>0.5264409184455872</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33971358</v>
+        <v>4822613</v>
       </c>
       <c r="Z3" t="n">
-        <v>1397302</v>
+        <v>198886</v>
       </c>
       <c r="AA3" t="n">
-        <v>60316</v>
+        <v>8613</v>
       </c>
       <c r="AB3" t="n">
-        <v>48014</v>
+        <v>6871</v>
       </c>
       <c r="AC3" t="n">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70672833</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>78184653</v>
+        <v>11155975</v>
       </c>
       <c r="AG3" t="n">
-        <v>90082731</v>
+        <v>12822698</v>
       </c>
       <c r="AH3" t="n">
-        <v>107728630</v>
+        <v>15345889</v>
       </c>
       <c r="AI3" t="n">
-        <v>114375588</v>
+        <v>16296043</v>
       </c>
       <c r="AJ3" t="n">
-        <v>111294621</v>
+        <v>15855549</v>
       </c>
       <c r="AK3" t="n">
-        <v>113767753</v>
+        <v>16209238</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575461745262146</v>
+        <v>0.9574265480041504</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099145531654358</v>
+        <v>0.9097204804420471</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572057485580444</v>
+        <v>0.8567676544189453</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6611488461494446</v>
+        <v>0.660255491733551</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014421701431274</v>
+        <v>0.9011561870574951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312224984169006</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06057714089168283</v>
+        <v>0.04999976264467169</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03190669178870938</v>
+        <v>0.0318933357951476</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4809582</v>
+        <v>988180</v>
       </c>
       <c r="E4" t="n">
-        <v>16864190</v>
+        <v>2056703</v>
       </c>
       <c r="F4" t="n">
-        <v>1222265</v>
+        <v>216433</v>
       </c>
       <c r="G4" t="n">
-        <v>66639</v>
+        <v>14829</v>
       </c>
       <c r="H4" t="n">
-        <v>114872</v>
+        <v>23236</v>
       </c>
       <c r="I4" t="n">
-        <v>12416</v>
+        <v>2496</v>
       </c>
       <c r="J4" t="n">
-        <v>477</v>
+        <v>76</v>
       </c>
       <c r="K4" t="n">
-        <v>5120963</v>
+        <v>1057751</v>
       </c>
       <c r="L4" t="n">
-        <v>6259549</v>
+        <v>1198758</v>
       </c>
       <c r="M4" t="n">
-        <v>2097633</v>
+        <v>395989</v>
       </c>
       <c r="N4" t="n">
-        <v>458295</v>
+        <v>108844</v>
       </c>
       <c r="O4" t="n">
-        <v>961322</v>
+        <v>183391</v>
       </c>
       <c r="P4" t="n">
-        <v>252910</v>
+        <v>41201</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999946355819702</v>
+        <v>0.9999939799308777</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8663469552993774</v>
+        <v>0.816092848777771</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7298348546028137</v>
+        <v>0.6272979974746704</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6355409622192383</v>
+        <v>0.5035058856010437</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3046087026596069</v>
+        <v>0.1262396723031998</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6964468359947205</v>
+        <v>0.5479902625083923</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7605093717575073</v>
+        <v>0.6053277254104614</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1449333</v>
+        <v>208181</v>
       </c>
       <c r="Z4" t="n">
-        <v>21009908</v>
+        <v>3003787</v>
       </c>
       <c r="AA4" t="n">
-        <v>583427</v>
+        <v>83142</v>
       </c>
       <c r="AB4" t="n">
-        <v>38798</v>
+        <v>5553</v>
       </c>
       <c r="AC4" t="n">
-        <v>8037</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1552232</v>
+        <v>222967</v>
       </c>
       <c r="AG4" t="n">
-        <v>2041690</v>
+        <v>291423</v>
       </c>
       <c r="AH4" t="n">
-        <v>931058</v>
+        <v>133032</v>
       </c>
       <c r="AI4" t="n">
-        <v>211876</v>
+        <v>30322</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349947</v>
+        <v>49989</v>
       </c>
       <c r="AK4" t="n">
-        <v>92788</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569248557090759</v>
+        <v>0.9566173553466797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106714725494385</v>
+        <v>0.9106400609016418</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575274348258972</v>
+        <v>0.8573110699653625</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614453196525574</v>
+        <v>0.6607382893562317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901680588722229</v>
+        <v>0.9015686511993408</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313349723815918</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>212412</v>
+        <v>49761</v>
       </c>
       <c r="E5" t="n">
-        <v>1635371</v>
+        <v>320746</v>
       </c>
       <c r="F5" t="n">
-        <v>4030110</v>
+        <v>448520</v>
       </c>
       <c r="G5" t="n">
-        <v>161924</v>
+        <v>33237</v>
       </c>
       <c r="H5" t="n">
-        <v>467158</v>
+        <v>75322</v>
       </c>
       <c r="I5" t="n">
-        <v>47694</v>
+        <v>9486</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4451823</v>
+        <v>835774</v>
       </c>
       <c r="L5" t="n">
-        <v>6225789</v>
+        <v>1245176</v>
       </c>
       <c r="M5" t="n">
-        <v>2524602</v>
+        <v>488559</v>
       </c>
       <c r="N5" t="n">
-        <v>431954</v>
+        <v>76263</v>
       </c>
       <c r="O5" t="n">
-        <v>1148981</v>
+        <v>248601</v>
       </c>
       <c r="P5" t="n">
-        <v>368000</v>
+        <v>91637</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999958872795105</v>
+        <v>0.9999953508377075</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9169132709503174</v>
+        <v>0.8846536874771118</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8916338682174683</v>
+        <v>0.8511248826980591</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9598814249038696</v>
+        <v>0.9461166858673096</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9922730922698975</v>
+        <v>0.9887239933013916</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9816836714744568</v>
+        <v>0.9736846685409546</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9946108460426331</v>
+        <v>0.9919080138206482</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56771</v>
+        <v>8150</v>
       </c>
       <c r="Z5" t="n">
-        <v>600397</v>
+        <v>86254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5618737</v>
+        <v>802859</v>
       </c>
       <c r="AB5" t="n">
-        <v>69930</v>
+        <v>9996</v>
       </c>
       <c r="AC5" t="n">
-        <v>204446</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1506157</v>
+        <v>214445</v>
       </c>
       <c r="AG5" t="n">
-        <v>2080071</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>935975</v>
+        <v>134220</v>
       </c>
       <c r="AI5" t="n">
-        <v>212438</v>
+        <v>30453</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351835</v>
+        <v>50456</v>
       </c>
       <c r="AK5" t="n">
-        <v>93115</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734547734260559</v>
+        <v>0.9733545184135437</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642252922058105</v>
+        <v>0.9640889763832092</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983795166015625</v>
+        <v>0.9837200045585632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963172078132629</v>
+        <v>0.9962978363037109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939088821411133</v>
+        <v>0.9938812851905823</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983864426612854</v>
+        <v>0.9983810186386108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>88678</v>
+        <v>16775</v>
       </c>
       <c r="E6" t="n">
-        <v>123874</v>
+        <v>21842</v>
       </c>
       <c r="F6" t="n">
-        <v>141752</v>
+        <v>26815</v>
       </c>
       <c r="G6" t="n">
-        <v>194982</v>
+        <v>13372</v>
       </c>
       <c r="H6" t="n">
-        <v>69150</v>
+        <v>9594</v>
       </c>
       <c r="I6" t="n">
-        <v>8419</v>
+        <v>1226</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45736</v>
+        <v>6580</v>
       </c>
       <c r="Z6" t="n">
-        <v>37747</v>
+        <v>5392</v>
       </c>
       <c r="AA6" t="n">
-        <v>76612</v>
+        <v>11005</v>
       </c>
       <c r="AB6" t="n">
-        <v>414498</v>
+        <v>59182</v>
       </c>
       <c r="AC6" t="n">
-        <v>48976</v>
+        <v>6995</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>10039</v>
+        <v>2983</v>
       </c>
       <c r="E7" t="n">
-        <v>175092</v>
+        <v>44825</v>
       </c>
       <c r="F7" t="n">
-        <v>582513</v>
+        <v>119326</v>
       </c>
       <c r="G7" t="n">
-        <v>197294</v>
+        <v>53532</v>
       </c>
       <c r="H7" t="n">
-        <v>2420851</v>
+        <v>261861</v>
       </c>
       <c r="I7" t="n">
-        <v>183899</v>
+        <v>27912</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>5677</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>208385</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53273</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3217997</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84304</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>174</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>252</v>
+        <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>13371</v>
+        <v>3694</v>
       </c>
       <c r="F8" t="n">
-        <v>33678</v>
+        <v>8857</v>
       </c>
       <c r="G8" t="n">
-        <v>17333</v>
+        <v>5156</v>
       </c>
       <c r="H8" t="n">
-        <v>303192</v>
+        <v>73849</v>
       </c>
       <c r="I8" t="n">
-        <v>985859</v>
+        <v>101870</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2318</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1861</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88173</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260744</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
